--- a/data/trans_dic/IP12B$garganta-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,73; 90,03</t>
+          <t>17,05; 87,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,95; 93,15</t>
+          <t>46,42; 93,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,04</t>
+          <t>0,0; 63,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,05</t>
+          <t>0,0; 58,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,46; 78,29</t>
+          <t>17,23; 77,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 59,41</t>
+          <t>13,49; 59,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,45; 77,37</t>
+          <t>41,25; 80,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 55,62</t>
+          <t>6,78; 58,74</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,27; 76,3</t>
+          <t>47,27; 75,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,58; 63,6</t>
+          <t>35,98; 64,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,58; 59,02</t>
+          <t>31,24; 58,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,48; 65,82</t>
+          <t>38,11; 65,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,52; 61,9</t>
+          <t>37,52; 62,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 58,95</t>
+          <t>31,99; 58,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,69; 68,92</t>
+          <t>47,63; 66,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,19; 60,66</t>
+          <t>40,59; 58,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,49; 54,88</t>
+          <t>35,3; 54,4</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,64; 58,61</t>
+          <t>8,75; 61,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,48; 59,95</t>
+          <t>21,14; 61,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38,75; 77,94</t>
+          <t>39,32; 77,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,57; 73,76</t>
+          <t>20,4; 73,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,75; 66,01</t>
+          <t>12,74; 64,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,89; 77,77</t>
+          <t>23,47; 78,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,11; 58,78</t>
+          <t>22,27; 59,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,27; 54,93</t>
+          <t>21,54; 54,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,29; 70,32</t>
+          <t>39,53; 71,84</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,51; 67,85</t>
+          <t>44,01; 68,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,82; 62,53</t>
+          <t>41,34; 61,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,69; 57,21</t>
+          <t>36,39; 58,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35,85; 58,92</t>
+          <t>34,77; 57,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,07; 58,52</t>
+          <t>36,72; 57,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,32; 57,36</t>
+          <t>33,47; 57,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,54; 58,98</t>
+          <t>42,59; 59,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,96; 56,64</t>
+          <t>41,8; 56,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,2; 53,8</t>
+          <t>38,53; 53,84</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3827</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>10540</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2203</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>964; 4918</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4671; 9370</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4169</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3233</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1214; 5440</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2239</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1505; 6625</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>7057; 13699</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>598; 5180</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>18677</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17669</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14078</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>16409</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>22806</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>16579</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35086</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>40475</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30657</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14006; 22421</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12612; 22746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>9939; 18720</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>11946; 20618</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>16997; 28119</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>11633; 21427</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>29043; 40627</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>32610; 47312</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>24071; 37092</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9954</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7354</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10321</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>14495</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>752; 5326</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3421; 10012</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6577; 12919</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2011; 7290</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1429; 7247</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2170; 7263</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4109; 10957</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5902; 14861</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10268; 18661</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>24550</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>31407</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25548</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>46267</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>61336</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>47354</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>19310; 29995</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25338; 37976</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20062; 32430</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>16241; 26946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>23341; 36335</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>16019; 27576</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>38578; 53788</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>52194; 70015</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>39679; 55447</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$garganta-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 87,0</t>
+          <t>15,65; 88,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,42; 93,13</t>
+          <t>46,72; 93,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,35</t>
+          <t>0,0; 63,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,74</t>
+          <t>0,0; 50,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,23; 77,19</t>
+          <t>10,62; 79,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 59,38</t>
+          <t>13,43; 63,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41,25; 80,07</t>
+          <t>42,89; 81,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 58,74</t>
+          <t>6,93; 57,19</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,27; 75,68</t>
+          <t>49,11; 76,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,98; 64,9</t>
+          <t>37,11; 64,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,24; 58,83</t>
+          <t>31,06; 59,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,11; 65,77</t>
+          <t>38,72; 69,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,52; 62,08</t>
+          <t>38,03; 62,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,99; 58,91</t>
+          <t>32,15; 58,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,63; 66,63</t>
+          <t>47,57; 67,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,59; 58,89</t>
+          <t>40,94; 59,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>35,3; 54,4</t>
+          <t>36,24; 55,64</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 61,96</t>
+          <t>8,62; 60,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 61,87</t>
+          <t>21,57; 61,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,32; 77,24</t>
+          <t>37,78; 77,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,4; 73,96</t>
+          <t>26,01; 74,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,74; 64,6</t>
+          <t>16,47; 65,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,47; 78,53</t>
+          <t>21,59; 77,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,27; 59,38</t>
+          <t>22,35; 57,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,54; 54,24</t>
+          <t>23,53; 54,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,53; 71,84</t>
+          <t>38,99; 70,65</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,01; 68,36</t>
+          <t>44,04; 68,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,34; 61,96</t>
+          <t>41,12; 62,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,39; 58,83</t>
+          <t>36,33; 56,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,77; 57,69</t>
+          <t>33,93; 58,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,72; 57,17</t>
+          <t>36,04; 57,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,47; 57,62</t>
+          <t>33,87; 57,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,59; 59,38</t>
+          <t>43,1; 60,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>41,8; 56,08</t>
+          <t>42,14; 56,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 53,84</t>
+          <t>37,95; 53,78</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de garganta, tos, catarro o gripe (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>964; 4918</t>
+          <t>885; 4996</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4671; 9370</t>
+          <t>4701; 9359</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 4147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3233</t>
+          <t>0; 2760</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1214; 5440</t>
+          <t>748; 5633</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1505; 6625</t>
+          <t>1498; 7130</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7057; 13699</t>
+          <t>7338; 13881</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>598; 5180</t>
+          <t>611; 5044</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14006; 22421</t>
+          <t>14551; 22731</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12612; 22746</t>
+          <t>13007; 22548</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9939; 18720</t>
+          <t>9883; 18807</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11946; 20618</t>
+          <t>12139; 21805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16997; 28119</t>
+          <t>17227; 28448</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11633; 21427</t>
+          <t>11693; 21318</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29043; 40627</t>
+          <t>29008; 41256</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32610; 47312</t>
+          <t>32893; 47615</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24071; 37092</t>
+          <t>24712; 37942</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>752; 5326</t>
+          <t>741; 5240</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3421; 10012</t>
+          <t>3491; 9884</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6577; 12919</t>
+          <t>6319; 13039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2011; 7290</t>
+          <t>2564; 7308</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1429; 7247</t>
+          <t>1848; 7356</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2170; 7263</t>
+          <t>1996; 7192</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4109; 10957</t>
+          <t>4124; 10576</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5902; 14861</t>
+          <t>6448; 14881</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10268; 18661</t>
+          <t>10128; 18350</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19310; 29995</t>
+          <t>19323; 29890</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25338; 37976</t>
+          <t>25203; 38201</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20062; 32430</t>
+          <t>20027; 31390</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16241; 26946</t>
+          <t>15846; 27115</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23341; 36335</t>
+          <t>22908; 36394</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16019; 27576</t>
+          <t>16210; 27319</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38578; 53788</t>
+          <t>39041; 54428</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52194; 70015</t>
+          <t>52614; 70406</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39679; 55447</t>
+          <t>39078; 55388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$garganta-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$garganta-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>30,61%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>55,79%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>73,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>23,06%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,22%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>44,84%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,65; 88,37</t>
+          <t>0,0; 50,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46,72; 93,02</t>
+          <t>18,46; 78,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,02</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,14</t>
+          <t>24,73; 90,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 79,92</t>
+          <t>46,95; 93,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 55,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,43; 63,91</t>
+          <t>12,56; 59,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42,89; 81,13</t>
+          <t>39,45; 77,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 57,19</t>
+          <t>6,7; 55,62</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50,35%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>45,58%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>63,04%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>50,41%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>44,24%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>52,35%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>50,35%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>45,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,11; 76,73</t>
+          <t>38,48; 65,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,11; 64,33</t>
+          <t>36,52; 61,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 59,1</t>
+          <t>32,13; 58,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,72; 69,56</t>
+          <t>49,27; 76,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,03; 62,81</t>
+          <t>35,58; 63,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,15; 58,61</t>
+          <t>31,58; 59,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,57; 67,66</t>
+          <t>47,69; 68,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,94; 59,26</t>
+          <t>41,19; 60,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,24; 55,64</t>
+          <t>35,49; 54,88</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47,03%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35,33%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>31,62%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>39,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>59,51%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,62; 60,95</t>
+          <t>20,57; 73,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,57; 61,08</t>
+          <t>12,75; 66,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,78; 77,96</t>
+          <t>22,89; 77,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26,01; 74,15</t>
+          <t>8,64; 58,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 65,57</t>
+          <t>19,48; 59,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,59; 77,76</t>
+          <t>38,75; 77,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,35; 57,31</t>
+          <t>22,11; 58,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,53; 54,31</t>
+          <t>23,27; 54,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,99; 70,65</t>
+          <t>39,29; 70,32</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>55,95%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>51,24%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>46,35%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,5%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44,04; 68,12</t>
+          <t>35,85; 58,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,12; 62,33</t>
+          <t>38,07; 58,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,33; 56,94</t>
+          <t>33,32; 57,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,93; 58,05</t>
+          <t>43,51; 67,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>36,04; 57,26</t>
+          <t>41,82; 62,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,87; 57,08</t>
+          <t>35,69; 57,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,1; 60,09</t>
+          <t>42,54; 58,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42,14; 56,39</t>
+          <t>41,96; 56,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,95; 53,78</t>
+          <t>38,2; 53,8</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3161</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>3154</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>7379</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1517</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3161</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>885; 4996</t>
+          <t>0; 2755</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4701; 9359</t>
+          <t>1301; 5518</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 2239</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2760</t>
+          <t>1398; 5089</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>748; 5633</t>
+          <t>4723; 9371</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2239</t>
+          <t>0; 3622</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1498; 7130</t>
+          <t>1401; 6628</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7338; 13881</t>
+          <t>6750; 13238</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>611; 5044</t>
+          <t>591; 4905</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>16409</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22806</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16579</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>18677</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17669</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14078</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16409</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22806</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16579</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14551; 22731</t>
+          <t>12063; 20633</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13007; 22548</t>
+          <t>16541; 28040</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9883; 18807</t>
+          <t>11686; 21439</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12139; 21805</t>
+          <t>14599; 22604</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17227; 28448</t>
+          <t>12470; 22291</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11693; 21318</t>
+          <t>10047; 18779</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29008; 41256</t>
+          <t>29081; 42024</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32893; 47615</t>
+          <t>33091; 48740</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24712; 37942</t>
+          <t>24200; 37419</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3963</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>2719</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>6358</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>9954</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4635</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3963</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4541</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>741; 5240</t>
+          <t>2027; 7270</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3491; 9884</t>
+          <t>1430; 7406</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6319; 13039</t>
+          <t>2117; 7193</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2564; 7308</t>
+          <t>742; 5039</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1848; 7356</t>
+          <t>3153; 9701</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1996; 7192</t>
+          <t>6482; 13036</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4124; 10576</t>
+          <t>4081; 10846</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6448; 14881</t>
+          <t>6375; 15051</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10128; 18350</t>
+          <t>10206; 18264</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>21716</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29929</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>21805</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>24550</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>31407</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>25548</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>21716</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29929</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21805</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19323; 29890</t>
+          <t>16742; 27521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25203; 38201</t>
+          <t>24197; 37194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20027; 31390</t>
+          <t>15946; 27450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15846; 27115</t>
+          <t>19092; 29770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22908; 36394</t>
+          <t>25632; 38324</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16210; 27319</t>
+          <t>19674; 31540</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39041; 54428</t>
+          <t>38531; 53426</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>52614; 70406</t>
+          <t>52393; 70713</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39078; 55388</t>
+          <t>39342; 55408</t>
         </is>
       </c>
     </row>
